--- a/Packages/cn.etetet.yiuilubangen/Luban/Release/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Release/Base/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31275" windowHeight="17040"/>
+    <workbookView windowWidth="21863" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -111,21 +111,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>StartMachine</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>StartProcess</t>
-  </si>
-  <si>
-    <t>StartScene</t>
-  </si>
-  <si>
-    <t>StartZone</t>
   </si>
 </sst>
 </file>
@@ -807,13 +792,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1075,20 +1053,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="13.8" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="16.125" customWidth="1"/>
-    <col min="2" max="2" width="29.375" customWidth="1"/>
+    <col min="1" max="1" width="16.1296296296296" customWidth="1"/>
+    <col min="2" max="2" width="29.3796296296296" customWidth="1"/>
     <col min="3" max="3" width="34.75" customWidth="1"/>
     <col min="4" max="4" width="35.25" customWidth="1"/>
-    <col min="5" max="5" width="23.625" customWidth="1"/>
-    <col min="6" max="6" width="99.375" customWidth="1"/>
-    <col min="7" max="7" width="18.375" customWidth="1"/>
-    <col min="8" max="8" width="21.375" customWidth="1"/>
-    <col min="9" max="9" width="35.125" customWidth="1"/>
-    <col min="10" max="10" width="24.125" customWidth="1"/>
+    <col min="5" max="5" width="23.6296296296296" customWidth="1"/>
+    <col min="6" max="6" width="99.3796296296296" customWidth="1"/>
+    <col min="7" max="7" width="18.3796296296296" customWidth="1"/>
+    <col min="8" max="8" width="21.3796296296296" customWidth="1"/>
+    <col min="9" max="9" width="35.1296296296296" customWidth="1"/>
+    <col min="10" max="10" width="24.1296296296296" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="12" max="12" width="38.375" customWidth="1"/>
+    <col min="12" max="12" width="38.3796296296296" customWidth="1"/>
     <col min="13" max="16384" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1186,112 +1164,28 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="str">
-        <f t="shared" ref="C4:C7" si="0">_xlfn.CONCAT(B4,"ConfigCategory")</f>
-        <v>StartMachineConfigCategory</v>
-      </c>
-      <c r="D4" t="str">
-        <f t="shared" ref="D4:D7" si="1">_xlfn.CONCAT(B4,"Config")</f>
-        <v>StartMachineConfig</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="str">
-        <f>_xlfn.CONCAT(B4,".xlsx")</f>
-        <v>StartMachine.xlsx</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
-      </c>
+    <row r="4" spans="12:12">
       <c r="L4" t="str">
-        <f t="shared" ref="L4:L7" si="2">_xlfn.CONCAT(C4)</f>
-        <v>StartMachineConfigCategory</v>
+        <f t="shared" ref="L4:L7" si="0">_xlfn.CONCAT(C4)</f>
+        <v/>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:12">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="str">
+    <row r="5" customFormat="1" spans="12:12">
+      <c r="L5" t="str">
         <f t="shared" si="0"/>
-        <v>StartProcessConfigCategory</v>
-      </c>
-      <c r="D5" t="str">
-        <f t="shared" si="1"/>
-        <v>StartProcessConfig</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="str">
-        <f>_xlfn.CONCAT(B5,".xlsx")</f>
-        <v>StartProcess.xlsx</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" t="str">
-        <f t="shared" si="2"/>
-        <v>StartProcessConfigCategory</v>
+        <v/>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:12">
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="str">
+    <row r="6" customFormat="1" spans="12:12">
+      <c r="L6" t="str">
         <f t="shared" si="0"/>
-        <v>StartSceneConfigCategory</v>
-      </c>
-      <c r="D6" t="str">
-        <f t="shared" si="1"/>
-        <v>StartSceneConfig</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="str">
-        <f>_xlfn.CONCAT(B6,".xlsx")</f>
-        <v>StartScene.xlsx</v>
-      </c>
-      <c r="I6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" t="str">
-        <f t="shared" si="2"/>
-        <v>StartSceneConfigCategory</v>
+        <v/>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="2:12">
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="str">
+    <row r="7" customFormat="1" spans="12:12">
+      <c r="L7" t="str">
         <f t="shared" si="0"/>
-        <v>StartZoneConfigCategory</v>
-      </c>
-      <c r="D7" t="str">
-        <f t="shared" si="1"/>
-        <v>StartZoneConfig</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="str">
-        <f>_xlfn.CONCAT(B7,".xlsx")</f>
-        <v>StartZone.xlsx</v>
-      </c>
-      <c r="I7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" t="str">
-        <f t="shared" si="2"/>
-        <v>StartZoneConfigCategory</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.yiuilubangen/Luban/Release/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Release/Base/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21863" windowHeight="12180"/>
+    <workbookView windowWidth="31275" windowHeight="17040"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,21 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>StartMachine</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>StartProcess</t>
+  </si>
+  <si>
+    <t>StartScene</t>
+  </si>
+  <si>
+    <t>StartZone</t>
   </si>
 </sst>
 </file>
@@ -792,6 +807,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1053,20 +1075,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="13.8" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="16.1296296296296" customWidth="1"/>
-    <col min="2" max="2" width="29.3796296296296" customWidth="1"/>
+    <col min="1" max="1" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="29.375" customWidth="1"/>
     <col min="3" max="3" width="34.75" customWidth="1"/>
     <col min="4" max="4" width="35.25" customWidth="1"/>
-    <col min="5" max="5" width="23.6296296296296" customWidth="1"/>
-    <col min="6" max="6" width="99.3796296296296" customWidth="1"/>
-    <col min="7" max="7" width="18.3796296296296" customWidth="1"/>
-    <col min="8" max="8" width="21.3796296296296" customWidth="1"/>
-    <col min="9" max="9" width="35.1296296296296" customWidth="1"/>
-    <col min="10" max="10" width="24.1296296296296" customWidth="1"/>
+    <col min="5" max="5" width="23.625" customWidth="1"/>
+    <col min="6" max="6" width="99.375" customWidth="1"/>
+    <col min="7" max="7" width="18.375" customWidth="1"/>
+    <col min="8" max="8" width="21.375" customWidth="1"/>
+    <col min="9" max="9" width="35.125" customWidth="1"/>
+    <col min="10" max="10" width="24.125" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="12" max="12" width="38.3796296296296" customWidth="1"/>
+    <col min="12" max="12" width="38.375" customWidth="1"/>
     <col min="13" max="16384" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1164,28 +1186,112 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="12:12">
+    <row r="4" spans="2:12">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" ref="C4:C7" si="0">_xlfn.CONCAT(B4,"ConfigCategory")</f>
+        <v>StartMachineConfigCategory</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" ref="D4:D7" si="1">_xlfn.CONCAT(B4,"Config")</f>
+        <v>StartMachineConfig</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <f>_xlfn.CONCAT(B4,".xlsx")</f>
+        <v>StartMachine.xlsx</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
       <c r="L4" t="str">
-        <f t="shared" ref="L4:L7" si="0">_xlfn.CONCAT(C4)</f>
-        <v/>
+        <f t="shared" ref="L4:L7" si="2">_xlfn.CONCAT(C4)</f>
+        <v>StartMachineConfigCategory</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="12:12">
+    <row r="5" customFormat="1" spans="2:12">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>StartProcessConfigCategory</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="1"/>
+        <v>StartProcessConfig</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <f>_xlfn.CONCAT(B5,".xlsx")</f>
+        <v>StartProcess.xlsx</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
       <c r="L5" t="str">
+        <f t="shared" si="2"/>
+        <v>StartProcessConfigCategory</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:12">
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>StartSceneConfigCategory</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="1"/>
+        <v>StartSceneConfig</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
+        <f>_xlfn.CONCAT(B6,".xlsx")</f>
+        <v>StartScene.xlsx</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="2"/>
+        <v>StartSceneConfigCategory</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="12:12">
-      <c r="L6" t="str">
+    <row r="7" customFormat="1" spans="2:12">
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="12:12">
+        <v>StartZoneConfigCategory</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="1"/>
+        <v>StartZoneConfig</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="str">
+        <f>_xlfn.CONCAT(B7,".xlsx")</f>
+        <v>StartZone.xlsx</v>
+      </c>
+      <c r="I7" t="s">
+        <v>29</v>
+      </c>
       <c r="L7" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>StartZoneConfigCategory</v>
       </c>
     </row>
   </sheetData>
